--- a/data/raw/GLNPO 2024 Spring/Ontario/D100/ON 60 D100 QA Spring 2024 24GO00Q53 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Ontario/D100/ON 60 D100 QA Spring 2024 24GO00Q53 Zoop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Ontario\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B32614-6172-4C1A-88A0-A7903021878F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE66B2BB-9593-4356-8204-213ABF396990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3797E256-CC4B-4E3E-BD78-76A0C66C6B42}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="41" r:id="rId2"/>
+    <pivotCache cacheId="25" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -336,7 +336,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -347,6 +347,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -365,7 +366,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Gl Lab User" refreshedDate="45544.67713935185" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="184" xr:uid="{654485B9-49DA-4492-A0C9-F493419832B6}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Chris Marshall" refreshedDate="46153.641015856483" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="184" xr:uid="{654485B9-49DA-4492-A0C9-F493419832B6}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:Q185" sheet="Sheet1"/>
   </cacheSource>
@@ -430,7 +431,7 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="LENGTH" numFmtId="0">
-      <sharedItems containsMixedTypes="1" containsNumber="1" minValue="0" maxValue="2.738"/>
+      <sharedItems containsMixedTypes="1" containsNumber="1" minValue="0.32200000000000001" maxValue="2.738"/>
     </cacheField>
     <cacheField name="SEX" numFmtId="0">
       <sharedItems/>
@@ -1927,7 +1928,7 @@
     <s v="DIYTHOM"/>
     <s v="CYC "/>
     <s v="COP"/>
-    <n v="0.86599999999999999"/>
+    <s v="NA"/>
     <s v="M"/>
     <n v="1"/>
   </r>
@@ -1965,7 +1966,7 @@
     <s v="DIYTHOM"/>
     <s v="CYC "/>
     <s v="COP"/>
-    <n v="0.83"/>
+    <s v="NA"/>
     <s v="M"/>
     <n v="1"/>
   </r>
@@ -1984,7 +1985,7 @@
     <s v="DIYTHOM"/>
     <s v="CYC "/>
     <s v="COP"/>
-    <n v="1.0449999999999999"/>
+    <s v="NA"/>
     <s v="F"/>
     <n v="1"/>
   </r>
@@ -2003,7 +2004,7 @@
     <s v="DIYTHOM"/>
     <s v="CYC "/>
     <s v="COP"/>
-    <n v="0.995"/>
+    <s v="NA"/>
     <s v="F"/>
     <n v="1"/>
   </r>
@@ -2041,7 +2042,7 @@
     <s v="DIYTHOM"/>
     <s v="CYC "/>
     <s v="COP"/>
-    <n v="1.022"/>
+    <s v="NA"/>
     <s v="F"/>
     <n v="1"/>
   </r>
@@ -2098,7 +2099,7 @@
     <s v="DIYTHOM"/>
     <s v="CYC "/>
     <s v="COP"/>
-    <n v="0.80500000000000005"/>
+    <s v="NA"/>
     <s v="M"/>
     <n v="1"/>
   </r>
@@ -2117,7 +2118,7 @@
     <s v="DIYTHOM"/>
     <s v="CYC "/>
     <s v="COP"/>
-    <n v="0.754"/>
+    <s v="NA"/>
     <s v="M"/>
     <n v="1"/>
   </r>
@@ -2231,7 +2232,7 @@
     <s v="DIYTHOM"/>
     <s v="CYC "/>
     <s v="COP"/>
-    <n v="0.89300000000000002"/>
+    <s v="NA"/>
     <s v="M"/>
     <n v="1"/>
   </r>
@@ -2345,7 +2346,7 @@
     <s v="DIYTHOM"/>
     <s v="CYC "/>
     <s v="COP"/>
-    <n v="0.98899999999999999"/>
+    <s v="NA"/>
     <s v="F"/>
     <n v="1"/>
   </r>
@@ -2364,7 +2365,7 @@
     <s v="DIYTHOM"/>
     <s v="CYC "/>
     <s v="COP"/>
-    <n v="0.78900000000000003"/>
+    <s v="NA"/>
     <s v="M"/>
     <n v="1"/>
   </r>
@@ -2440,7 +2441,7 @@
     <s v="DIYTHOM"/>
     <s v="CYC "/>
     <s v="COP"/>
-    <n v="0.78600000000000003"/>
+    <s v="NA"/>
     <s v="M"/>
     <n v="1"/>
   </r>
@@ -2497,7 +2498,7 @@
     <s v="DIYTHOM"/>
     <s v="CYC "/>
     <s v="COP"/>
-    <n v="0.73499999999999999"/>
+    <s v="NA"/>
     <s v="M"/>
     <n v="1"/>
   </r>
@@ -2516,7 +2517,7 @@
     <s v="LEOMINU"/>
     <s v="CAL"/>
     <s v="COP"/>
-    <n v="0.94399999999999995"/>
+    <s v="NA"/>
     <s v="M"/>
     <n v="1"/>
   </r>
@@ -2554,7 +2555,7 @@
     <s v="DIYTHOM"/>
     <s v="CYC "/>
     <s v="COP"/>
-    <n v="0.82199999999999995"/>
+    <s v="NA"/>
     <s v="M"/>
     <n v="1"/>
   </r>
@@ -2611,7 +2612,7 @@
     <s v="DIYTHOM"/>
     <s v="CYC "/>
     <s v="COP"/>
-    <n v="0.999"/>
+    <s v="NA"/>
     <s v="F"/>
     <n v="1"/>
   </r>
@@ -2631,7 +2632,7 @@
     <s v="CAL"/>
     <s v="COP"/>
     <n v="1.0529999999999999"/>
-    <s v="NA"/>
+    <s v="M"/>
     <n v="1"/>
   </r>
   <r>
@@ -2744,7 +2745,7 @@
     <s v="LEOMINU"/>
     <s v="CAL"/>
     <s v="COP"/>
-    <n v="0.94199999999999995"/>
+    <s v="NA"/>
     <s v="F"/>
     <n v="1"/>
   </r>
@@ -3067,7 +3068,7 @@
     <s v="DAPSP"/>
     <s v="DAP"/>
     <s v="CLA"/>
-    <s v="CLA"/>
+    <s v="NA"/>
     <s v="NA"/>
     <n v="1"/>
   </r>
@@ -3276,7 +3277,7 @@
     <s v="CYCCOPE"/>
     <s v="CYCIMM"/>
     <s v="IMM"/>
-    <n v="0"/>
+    <s v="NA"/>
     <s v="NA"/>
     <n v="6"/>
   </r>
@@ -3295,7 +3296,7 @@
     <s v="DIACOPE"/>
     <s v="CALIMM"/>
     <s v="IMM"/>
-    <n v="4.0000000000000001E-3"/>
+    <s v="NA"/>
     <s v="NA"/>
     <n v="1"/>
   </r>
@@ -3314,7 +3315,7 @@
     <s v="DIYTHOM"/>
     <s v="CYC "/>
     <s v="COP"/>
-    <n v="0"/>
+    <s v="NA"/>
     <s v="M"/>
     <n v="2"/>
   </r>
@@ -3333,7 +3334,7 @@
     <s v="DIYTHOM"/>
     <s v="CYC "/>
     <s v="COP"/>
-    <n v="0"/>
+    <s v="NA"/>
     <s v="F"/>
     <n v="1"/>
   </r>
@@ -3523,7 +3524,7 @@
     <s v="SKIOREG"/>
     <s v="CAL"/>
     <s v="COP"/>
-    <n v="1.155"/>
+    <s v="NA"/>
     <s v="M"/>
     <n v="1"/>
   </r>
@@ -3542,7 +3543,7 @@
     <s v="SKIOREG"/>
     <s v="CAL"/>
     <s v="COP"/>
-    <n v="1.17"/>
+    <s v="NA"/>
     <s v="F"/>
     <n v="1"/>
   </r>
@@ -3599,7 +3600,7 @@
     <s v="SKIOREG"/>
     <s v="CAL"/>
     <s v="COP"/>
-    <n v="1.25"/>
+    <s v="NA"/>
     <s v="M"/>
     <n v="1"/>
   </r>
@@ -3637,7 +3638,7 @@
     <s v="SKIOREG"/>
     <s v="CAL"/>
     <s v="COP"/>
-    <n v="1.238"/>
+    <s v="NA"/>
     <s v="F"/>
     <n v="1"/>
   </r>
@@ -3656,7 +3657,7 @@
     <s v="SKIOREG"/>
     <s v="CAL"/>
     <s v="COP"/>
-    <n v="1.321"/>
+    <s v="NA"/>
     <s v="F"/>
     <n v="1"/>
   </r>
@@ -3694,7 +3695,7 @@
     <s v="SKIOREG"/>
     <s v="CAL"/>
     <s v="COP"/>
-    <n v="1.3979999999999999"/>
+    <s v="NA"/>
     <s v="F"/>
     <n v="1"/>
   </r>
@@ -3713,7 +3714,7 @@
     <s v="SKIOREG"/>
     <s v="CAL"/>
     <s v="COP"/>
-    <n v="1.3009999999999999"/>
+    <s v="NA"/>
     <s v="F"/>
     <n v="1"/>
   </r>
@@ -3732,7 +3733,7 @@
     <s v="SKIOREG"/>
     <s v="CAL"/>
     <s v="COP"/>
-    <n v="1.272"/>
+    <s v="NA"/>
     <s v="M"/>
     <n v="1"/>
   </r>
@@ -3751,7 +3752,7 @@
     <s v="SKIOREG"/>
     <s v="CAL"/>
     <s v="COP"/>
-    <n v="1.2829999999999999"/>
+    <s v="NA"/>
     <s v="F"/>
     <n v="1"/>
   </r>
@@ -3789,7 +3790,7 @@
     <s v="SKIOREG"/>
     <s v="CAL"/>
     <s v="COP"/>
-    <n v="1.3759999999999999"/>
+    <s v="NA"/>
     <s v="F"/>
     <n v="1"/>
   </r>
@@ -3851,10 +3852,10 @@
     <n v="0"/>
   </r>
   <r>
-    <s v="24GO00Q54"/>
-    <s v="ON 60"/>
-    <s v="D100"/>
-    <s v="24GO00I54"/>
+    <s v="24GO00Q53"/>
+    <s v="ON 60"/>
+    <s v="D100"/>
+    <s v="24GO00I53"/>
     <x v="1"/>
     <n v="256"/>
     <s v="CTH"/>
@@ -3870,10 +3871,10 @@
     <n v="0"/>
   </r>
   <r>
-    <s v="24GO00Q55"/>
-    <s v="ON 60"/>
-    <s v="D100"/>
-    <s v="24GO00I55"/>
+    <s v="24GO00Q53"/>
+    <s v="ON 60"/>
+    <s v="D100"/>
+    <s v="24GO00I53"/>
     <x v="2"/>
     <n v="128"/>
     <s v="CTH"/>
@@ -3913,7 +3914,7 @@
     <s v="D100"/>
     <s v="24GO00I53"/>
     <x v="2"/>
-    <n v="256"/>
+    <n v="128"/>
     <s v="CTH"/>
     <s v="NA"/>
     <s v="LINNAEUS"/>
@@ -3932,7 +3933,7 @@
     <s v="D100"/>
     <s v="24GO00I53"/>
     <x v="2"/>
-    <n v="256"/>
+    <n v="128"/>
     <s v="CTH"/>
     <s v="NA"/>
     <s v="LINNAEUS"/>
@@ -3949,7 +3950,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FAD35086-4977-42DF-8782-4E3051AFB834}" name="PivotTable2" cacheId="41" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FAD35086-4977-42DF-8782-4E3051AFB834}" name="PivotTable2" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="T2:Y15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField showAll="0"/>
@@ -4386,19 +4387,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB8AA08D-DE49-4338-A2A0-104A698CCB3C}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Y185"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="3" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="2.44140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="2.21875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
@@ -4454,7 +4455,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -4513,7 +4514,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>66</v>
       </c>
@@ -4584,7 +4585,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>66</v>
       </c>
@@ -4639,20 +4640,21 @@
       <c r="T4" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="8">
         <v>4</v>
       </c>
-      <c r="V4">
+      <c r="V4" s="8">
         <v>4</v>
       </c>
-      <c r="W4">
+      <c r="W4" s="8">
         <v>2</v>
       </c>
-      <c r="Y4">
+      <c r="X4" s="8"/>
+      <c r="Y4" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>66</v>
       </c>
@@ -4707,13 +4709,15 @@
       <c r="T5" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="8">
         <v>73</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="8">
         <v>64</v>
       </c>
-      <c r="Y5">
+      <c r="W5" s="8"/>
+      <c r="X5" s="8"/>
+      <c r="Y5" s="8">
         <v>137</v>
       </c>
     </row>
@@ -4772,20 +4776,21 @@
       <c r="T6" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="U6">
-        <v>1</v>
-      </c>
-      <c r="V6">
+      <c r="U6" s="8">
+        <v>1</v>
+      </c>
+      <c r="V6" s="8">
         <v>3</v>
       </c>
-      <c r="W6">
-        <v>1</v>
-      </c>
-      <c r="Y6">
+      <c r="W6" s="8">
+        <v>1</v>
+      </c>
+      <c r="X6" s="8"/>
+      <c r="Y6" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>66</v>
       </c>
@@ -4840,17 +4845,19 @@
       <c r="T7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="U7">
+      <c r="U7" s="8">
         <v>34</v>
       </c>
-      <c r="V7">
+      <c r="V7" s="8">
         <v>46</v>
       </c>
-      <c r="Y7">
+      <c r="W7" s="8"/>
+      <c r="X7" s="8"/>
+      <c r="Y7" s="8">
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -4905,20 +4912,21 @@
       <c r="T8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="U8">
+      <c r="U8" s="8">
         <v>20</v>
       </c>
-      <c r="V8">
+      <c r="V8" s="8">
         <v>10</v>
       </c>
-      <c r="W8">
+      <c r="W8" s="8">
         <v>28</v>
       </c>
-      <c r="Y8">
+      <c r="X8" s="8"/>
+      <c r="Y8" s="8">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>66</v>
       </c>
@@ -4973,20 +4981,21 @@
       <c r="T9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="U9">
+      <c r="U9" s="8">
         <v>0</v>
       </c>
-      <c r="V9">
+      <c r="V9" s="8">
         <v>2</v>
       </c>
-      <c r="W9">
+      <c r="W9" s="8">
         <v>0</v>
       </c>
-      <c r="Y9">
+      <c r="X9" s="8"/>
+      <c r="Y9" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>66</v>
       </c>
@@ -5041,20 +5050,21 @@
       <c r="T10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="U10">
-        <v>21</v>
-      </c>
-      <c r="V10">
+      <c r="U10" s="8">
+        <v>21</v>
+      </c>
+      <c r="V10" s="8">
         <v>16</v>
       </c>
-      <c r="W10">
+      <c r="W10" s="8">
         <v>0</v>
       </c>
-      <c r="Y10">
+      <c r="X10" s="8"/>
+      <c r="Y10" s="8">
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>66</v>
       </c>
@@ -5109,20 +5119,21 @@
       <c r="T11" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="U11">
+      <c r="U11" s="8">
         <v>3</v>
       </c>
-      <c r="V11">
-        <v>1</v>
-      </c>
-      <c r="W11">
+      <c r="V11" s="8">
+        <v>1</v>
+      </c>
+      <c r="W11" s="8">
         <v>2</v>
       </c>
-      <c r="Y11">
+      <c r="X11" s="8"/>
+      <c r="Y11" s="8">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -5177,20 +5188,21 @@
       <c r="T12" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="U12">
+      <c r="U12" s="8">
         <v>11</v>
       </c>
-      <c r="V12">
+      <c r="V12" s="8">
         <v>5</v>
       </c>
-      <c r="W12">
+      <c r="W12" s="8">
         <v>14</v>
       </c>
-      <c r="Y12">
+      <c r="X12" s="8"/>
+      <c r="Y12" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>66</v>
       </c>
@@ -5245,23 +5257,23 @@
       <c r="T13" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="U13">
-        <v>1</v>
-      </c>
-      <c r="V13">
+      <c r="U13" s="8">
+        <v>1</v>
+      </c>
+      <c r="V13" s="8">
         <v>0</v>
       </c>
-      <c r="W13">
+      <c r="W13" s="8">
         <v>3</v>
       </c>
-      <c r="X13">
-        <v>1</v>
-      </c>
-      <c r="Y13">
+      <c r="X13" s="8">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>66</v>
       </c>
@@ -5316,20 +5328,21 @@
       <c r="T14" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="U14">
-        <v>1</v>
-      </c>
-      <c r="V14">
-        <v>1</v>
-      </c>
-      <c r="W14">
+      <c r="U14" s="8">
+        <v>1</v>
+      </c>
+      <c r="V14" s="8">
+        <v>1</v>
+      </c>
+      <c r="W14" s="8">
         <v>0</v>
       </c>
-      <c r="Y14">
+      <c r="X14" s="8"/>
+      <c r="Y14" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -5384,23 +5397,23 @@
       <c r="T15" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="U15">
+      <c r="U15" s="8">
         <v>169</v>
       </c>
-      <c r="V15">
+      <c r="V15" s="8">
         <v>152</v>
       </c>
-      <c r="W15">
+      <c r="W15" s="8">
         <v>50</v>
       </c>
-      <c r="X15">
-        <v>1</v>
-      </c>
-      <c r="Y15">
+      <c r="X15" s="8">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="8">
         <v>372</v>
       </c>
     </row>
-    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>66</v>
       </c>
@@ -5453,7 +5466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>66</v>
       </c>
@@ -5515,7 +5528,7 @@
         <v>0.998</v>
       </c>
     </row>
-    <row r="18" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>66</v>
       </c>
@@ -5575,7 +5588,7 @@
         <v>0.997</v>
       </c>
     </row>
-    <row r="19" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>66</v>
       </c>
@@ -5697,7 +5710,7 @@
         <v>0.996</v>
       </c>
     </row>
-    <row r="21" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>66</v>
       </c>
@@ -5757,7 +5770,7 @@
       </c>
       <c r="V21" s="7"/>
     </row>
-    <row r="22" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>66</v>
       </c>
@@ -5817,7 +5830,7 @@
       </c>
       <c r="V22" s="7"/>
     </row>
-    <row r="23" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>66</v>
       </c>
@@ -5874,7 +5887,7 @@
       </c>
       <c r="U23" s="7"/>
     </row>
-    <row r="24" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>66</v>
       </c>
@@ -5927,7 +5940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>66</v>
       </c>
@@ -5980,7 +5993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>66</v>
       </c>
@@ -6033,7 +6046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -6086,7 +6099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -6139,7 +6152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>66</v>
       </c>
@@ -6192,7 +6205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -6245,7 +6258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -6298,7 +6311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -6351,7 +6364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>66</v>
       </c>
@@ -6404,7 +6417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>66</v>
       </c>
@@ -6457,7 +6470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>66</v>
       </c>
@@ -6510,7 +6523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>66</v>
       </c>
@@ -6563,7 +6576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>66</v>
       </c>
@@ -6616,7 +6629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>66</v>
       </c>
@@ -6669,7 +6682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>66</v>
       </c>
@@ -6722,7 +6735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>66</v>
       </c>
@@ -6775,7 +6788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>66</v>
       </c>
@@ -6828,7 +6841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>66</v>
       </c>
@@ -6881,7 +6894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>66</v>
       </c>
@@ -6934,7 +6947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>66</v>
       </c>
@@ -6987,7 +7000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>66</v>
       </c>
@@ -7040,7 +7053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>66</v>
       </c>
@@ -7093,7 +7106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>66</v>
       </c>
@@ -7146,7 +7159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>66</v>
       </c>
@@ -7199,7 +7212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>66</v>
       </c>
@@ -7252,7 +7265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>66</v>
       </c>
@@ -7305,7 +7318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>66</v>
       </c>
@@ -7358,7 +7371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>66</v>
       </c>
@@ -7464,7 +7477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>66</v>
       </c>
@@ -7517,7 +7530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>66</v>
       </c>
@@ -7570,7 +7583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>66</v>
       </c>
@@ -7623,7 +7636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>66</v>
       </c>
@@ -7676,7 +7689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>66</v>
       </c>
@@ -7729,7 +7742,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>66</v>
       </c>
@@ -7782,7 +7795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>66</v>
       </c>
@@ -7835,7 +7848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>66</v>
       </c>
@@ -7888,7 +7901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>66</v>
       </c>
@@ -7941,7 +7954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>66</v>
       </c>
@@ -7994,7 +8007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>66</v>
       </c>
@@ -8153,7 +8166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>66</v>
       </c>
@@ -8206,7 +8219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -8312,7 +8325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>66</v>
       </c>
@@ -8365,7 +8378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>66</v>
       </c>
@@ -8418,7 +8431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>66</v>
       </c>
@@ -8471,7 +8484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>66</v>
       </c>
@@ -8524,7 +8537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>66</v>
       </c>
@@ -8577,7 +8590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>66</v>
       </c>
@@ -8630,7 +8643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>66</v>
       </c>
@@ -8683,7 +8696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>66</v>
       </c>
@@ -8736,7 +8749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>66</v>
       </c>
@@ -8789,7 +8802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>66</v>
       </c>
@@ -8842,7 +8855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>66</v>
       </c>
@@ -8895,7 +8908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>66</v>
       </c>
@@ -8948,7 +8961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>66</v>
       </c>
@@ -9001,7 +9014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>66</v>
       </c>
@@ -9054,7 +9067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>66</v>
       </c>
@@ -9107,7 +9120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>66</v>
       </c>
@@ -9213,7 +9226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>66</v>
       </c>
@@ -9266,7 +9279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>66</v>
       </c>
@@ -9319,7 +9332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>66</v>
       </c>
@@ -9372,7 +9385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>66</v>
       </c>
@@ -9425,7 +9438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>66</v>
       </c>
@@ -9478,7 +9491,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>66</v>
       </c>
@@ -9531,7 +9544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>66</v>
       </c>
@@ -9584,7 +9597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>66</v>
       </c>
@@ -9637,7 +9650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>66</v>
       </c>
@@ -9690,7 +9703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>66</v>
       </c>
@@ -9743,7 +9756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>66</v>
       </c>
@@ -9796,7 +9809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>66</v>
       </c>
@@ -9849,7 +9862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>66</v>
       </c>
@@ -9902,7 +9915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>66</v>
       </c>
@@ -9955,7 +9968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>66</v>
       </c>
@@ -10008,7 +10021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>66</v>
       </c>
@@ -10061,7 +10074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>66</v>
       </c>
@@ -10114,7 +10127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>66</v>
       </c>
@@ -10167,7 +10180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>66</v>
       </c>
@@ -10220,7 +10233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>66</v>
       </c>
@@ -10273,7 +10286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>66</v>
       </c>
@@ -10326,7 +10339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>66</v>
       </c>
@@ -10379,7 +10392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>66</v>
       </c>
@@ -10432,7 +10445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>66</v>
       </c>
@@ -10485,7 +10498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>66</v>
       </c>
@@ -10538,7 +10551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>66</v>
       </c>
@@ -10644,7 +10657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>66</v>
       </c>
@@ -10697,7 +10710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>66</v>
       </c>
@@ -10909,7 +10922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>66</v>
       </c>
@@ -10962,7 +10975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>66</v>
       </c>
@@ -11015,7 +11028,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>66</v>
       </c>
@@ -11068,7 +11081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>66</v>
       </c>
@@ -11280,7 +11293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>66</v>
       </c>
@@ -11333,7 +11346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>66</v>
       </c>
@@ -11386,7 +11399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>66</v>
       </c>
@@ -11439,7 +11452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>66</v>
       </c>
@@ -11492,7 +11505,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>66</v>
       </c>
@@ -11545,7 +11558,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>66</v>
       </c>
@@ -11598,7 +11611,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>66</v>
       </c>
@@ -11651,7 +11664,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>66</v>
       </c>
@@ -11704,7 +11717,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>66</v>
       </c>
@@ -11757,7 +11770,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>66</v>
       </c>
@@ -11863,7 +11876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>66</v>
       </c>
@@ -11916,7 +11929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>66</v>
       </c>
@@ -11969,7 +11982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>66</v>
       </c>
@@ -12022,7 +12035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>66</v>
       </c>
@@ -12075,7 +12088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>66</v>
       </c>
@@ -12181,7 +12194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>66</v>
       </c>
@@ -12234,7 +12247,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>66</v>
       </c>
@@ -12287,7 +12300,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>66</v>
       </c>
@@ -12340,7 +12353,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>66</v>
       </c>
@@ -12393,7 +12406,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>66</v>
       </c>
@@ -12446,7 +12459,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>66</v>
       </c>
@@ -12499,7 +12512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="149" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>66</v>
       </c>
@@ -12552,7 +12565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>66</v>
       </c>
@@ -12605,7 +12618,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>66</v>
       </c>
@@ -12658,7 +12671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>66</v>
       </c>
@@ -12711,7 +12724,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>66</v>
       </c>
@@ -12817,7 +12830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>66</v>
       </c>
@@ -12923,7 +12936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>66</v>
       </c>
@@ -13029,7 +13042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>66</v>
       </c>
@@ -13082,7 +13095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>66</v>
       </c>
@@ -13188,7 +13201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>66</v>
       </c>
@@ -13347,7 +13360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>66</v>
       </c>
@@ -13403,7 +13416,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="166" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>66</v>
       </c>
@@ -13509,7 +13522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>66</v>
       </c>
@@ -13668,7 +13681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>66</v>
       </c>
@@ -13933,7 +13946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>66</v>
       </c>
@@ -14039,7 +14052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>66</v>
       </c>
@@ -14092,7 +14105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>66</v>
       </c>
@@ -14145,7 +14158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A180" s="5" t="s">
         <v>66</v>
       </c>
@@ -14199,7 +14212,7 @@
       </c>
       <c r="R180" s="5"/>
     </row>
-    <row r="181" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A181" s="5" t="s">
         <v>66</v>
       </c>
@@ -14253,7 +14266,7 @@
       </c>
       <c r="R181" s="5"/>
     </row>
-    <row r="182" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A182" s="5" t="s">
         <v>66</v>
       </c>
@@ -14307,7 +14320,7 @@
       </c>
       <c r="R182" s="5"/>
     </row>
-    <row r="183" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A183" s="5" t="s">
         <v>66</v>
       </c>
@@ -14360,7 +14373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A184" s="5" t="s">
         <v>66</v>
       </c>
@@ -14413,7 +14426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A185" s="5" t="s">
         <v>66</v>
       </c>
@@ -14467,16 +14480,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R185" xr:uid="{EB8AA08D-DE49-4338-A2A0-104A698CCB3C}">
-    <filterColumn colId="10">
-      <filters>
-        <filter val="Skistodiaptomus oregonensis"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A16:R176">
-      <sortCondition ref="L1:L185"/>
-    </sortState>
-  </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
